--- a/Data/CNEIO/Modifiable Shuttle - Trailblazer - 3717560080/1.6/Modifiable Shuttle - Trailblazer - 3717560080.xlsx
+++ b/Data/CNEIO/Modifiable Shuttle - Trailblazer - 3717560080/1.6/Modifiable Shuttle - Trailblazer - 3717560080.xlsx
@@ -5,16 +5,21 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\optol\OneDrive\바탕 화면\rimpy\translate\완성\Modifiable Shuttle - Trailblazer - 3717560080\1.6\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\optol\OneDrive\바탕 화면\test\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49141402-8E35-4682-92AE-E1EC2B79E834}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61FBE864-5A5C-4D6D-9F8C-3D472F6BE8F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6735" yWindow="4425" windowWidth="35670" windowHeight="25710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10920" yWindow="2340" windowWidth="35670" windowHeight="25710" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="chi" sheetId="2" r:id="rId2"/>
+    <sheet name="eng" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">chi!$A$1:$A$148</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
@@ -25,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="656" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1686" uniqueCount="699">
   <si>
     <t>Class+Node [(Identifier (Key)]</t>
   </si>
@@ -1233,12 +1238,6 @@
     <t>엔진 업그레이드</t>
   </si>
   <si>
-    <t>반중력 코어</t>
-  </si>
-  <si>
-    <t>반중력 발전기</t>
-  </si>
-  <si>
     <t>초능력 탐지 배열</t>
   </si>
   <si>
@@ -1248,9 +1247,6 @@
     <t>대형 포탑 거치대</t>
   </si>
   <si>
-    <t>소형 포탑 거치대</t>
-  </si>
-  <si>
     <t>업그레이드</t>
   </si>
   <si>
@@ -1315,9 +1311,6 @@
   </si>
   <si>
     <t>포탑 조준 시간</t>
-  </si>
-  <si>
-    <t>포탑 재사용 대기시간</t>
   </si>
   <si>
     <t>초능력 탐지 배열 활성화됨</t>
@@ -1457,9 +1450,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>보호막 코어</t>
-  </si>
-  <si>
     <t>보호막 충전 속도</t>
   </si>
   <si>
@@ -1487,10 +1477,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>비행 속도</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>이 지도의 새로운 위치로 왕복선을 순간이동시킵니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1535,14 +1521,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>보조 추진기를 탑재하고 기존 부품을 최적화합니다. \n\n연료 소모량이 다소 증가하는 대신, 최대 비행 거리와 이동 속도를 대폭 향상시키고 발사 대기 시간을 단축합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>반중력 기술 모듈을 탑재합니다. \n\n왕복선의 연료 소모율을 줄이는 동시에, 최대 비행 거리와 적재 용량이 비약적으로 증가합니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>전방향 편향 보호막 발생기를 탑재합니다. \n\n활성화 시 왕복선을 감싸는 구형 에너지 역장을 형성하여, 모든 방향에서 날아오는 고속 투사체를 효과적으로 차단하고 굴절시킵니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1551,22 +1529,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>3x3 대형 무기 거치대를 탑재합니다. \n\n대형 포탑을 설치할 수 있게 되며 사격 통제 효율 또한 높입니다. 소형 거치대 업그레이드와 동시에 설치할 수 없습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2x2 중형 무기 거치대를 탑재합니다. \n\n중소형 포탑을 설치할 수 있게 되며 사격 통제 효율 또한 높입니다. 대형 거치대 업그레이드와 동시에 설치할 수 없습니다.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>업그레이드 목록</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>비행 사정거리</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>전력 출력량</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1596,6 +1562,897 @@
   </si>
   <si>
     <t>개척자 왕복선 (착륙 중)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>English [Translation]</t>
+  </si>
+  <si>
+    <t>ChineseSimplified (简体中文) [Source string]</t>
+  </si>
+  <si>
+    <t>ChineseSimplified (简体中文) [Translation]</t>
+  </si>
+  <si>
+    <t>为穿梭机升级</t>
+  </si>
+  <si>
+    <t>移除穿梭机升级</t>
+  </si>
+  <si>
+    <t>为穿梭机安装炮塔</t>
+  </si>
+  <si>
+    <t>移除穿梭机炮塔</t>
+  </si>
+  <si>
+    <t>补充穿梭机炮塔弹药</t>
+  </si>
+  <si>
+    <t>开拓者号穿梭机</t>
+  </si>
+  <si>
+    <t>经由精心设计的先进穿梭机，初始状态下便有优越的性能，在运输与作战任务上均有出色表现。\n\n其高度预留的模块化架构支持从发动机大修到炮塔安装的广泛升级，进一步提高性能。\n\n——愿此行，终抵群星。</t>
+  </si>
+  <si>
+    <t>开拓者号穿梭机（降落中）</t>
+  </si>
+  <si>
+    <t>开拓者号穿梭机（起飞中）</t>
+  </si>
+  <si>
+    <t>引擎升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_Engine.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_Engine.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成辅助推进器并优化现有组件。\n\n显著提升最大航程与飞行速度，缩短发射冷却周期，但会增加燃料消耗</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_Engine.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_Engine.effectDescription</t>
+  </si>
+  <si>
+    <t>每级加成：飞行距离 ×1.2，速度 ×1.25，发射冷却减少 1250 tick，燃料消耗 ×1.1。</t>
+  </si>
+  <si>
+    <t>逆重核心升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_AntigravCore.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_AntigravCore.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成逆重科技模块。\n\n大幅提升穿梭机的最大航程与货舱载荷，同时降低运作时的燃料消耗率</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_AntigravCore.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_AntigravCore.effectDescription</t>
+  </si>
+  <si>
+    <t>每级加成：飞行距离 ×1.05，载货量 ×1.25，燃料消耗 ×0.8。</t>
+  </si>
+  <si>
+    <t>护盾发生器升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_Shield.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_Shield.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成全向偏导护盾发生器。\n\n激活后形成球形力场，能够有效拦截并偏转任何角度的高速投射物与局部爆炸冲击</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_Shield.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_Shield.effectDescription</t>
+  </si>
+  <si>
+    <t>每级加成：护盾容量 +1000，充能速率 +36/秒，护盾重构所需时间 -5秒。</t>
+  </si>
+  <si>
+    <t>逆重能源升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_AntigravPower.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_AntigravPower.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成反重力微型发电机组。\n\n为穿梭机电网及各子系统提供持续稳定的电力输出</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_AntigravPower.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_AntigravPower.effectDescription</t>
+  </si>
+  <si>
+    <t>停泊时生效。每级加成：电网输出功率 +2000W。</t>
+  </si>
+  <si>
+    <t>灵能探测阵列升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_PsychicDetection.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_PsychicDetection.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成反心灵隐身探测阵列。\n\n释放广域灵能扫描波，持续侦测并强制揭露有效范围内的隐身单位。\n\n此外，该阵列强大的信号干扰能力使航天飞机能够绕过轨道贸易防御系统，无需信号干扰器也可进行进攻</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_PsychicDetection.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_PsychicDetection.effectDescription</t>
+  </si>
+  <si>
+    <t>持续揭露穿梭机周围 19.9 格半径内的隐形实体。</t>
+  </si>
+  <si>
+    <t>指挥信号升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_SignalExtension.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_SignalExtension.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成机控中枢信号发生器。\n\n将穿梭机作为移动中继站，大幅延伸机械师对机械体的指挥信号范围</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_SignalExtension.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_SignalExtension.effectDescription</t>
+  </si>
+  <si>
+    <t>以穿梭机为中心生成额外的机械族指挥区域。\n\n每级加成：覆盖半径 +10 格。满级（5级）时覆盖全图。</t>
+  </si>
+  <si>
+    <t>跃迁引擎升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_Jump.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_Jump.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成定制启灵神经回路。\n\n使穿梭机能与超凡智能产生瞬时同频共振，从而实现短途空间跃迁</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_Jump.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_Jump.effectDescription</t>
+  </si>
+  <si>
+    <t>允许在本地图内进行瞬间传送。升级可进一步缩短冷却时间。</t>
+  </si>
+  <si>
+    <t>大型炮塔基座升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_TurretMount_Large.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_TurretMount_Large.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成3×3规格的大型武器基座。\n\n允许搭载重型炮塔并强化其火控效能。与小型基座升级互斥</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_TurretMount_Large.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_TurretMount_Large.effectDescription</t>
+  </si>
+  <si>
+    <t>允许安装一座 3x3 大小炮塔。\n\n固定负面效果: -20%载货量, +10%燃料消耗 。1级后每级加成：预热与冷却时间 -25%。</t>
+  </si>
+  <si>
+    <t>小型炮塔基座升级</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_TurretMount_Small.upgradeLabel</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_TurretMount_Small.upgradeLabel</t>
+  </si>
+  <si>
+    <t>集成2×2规格的中型武器基座。\n\n允许搭载中型炮塔并强化其火控效能。与大型基座升级互斥</t>
+  </si>
+  <si>
+    <t>Trailblazer.UpgradeDef+TB_Upgrade_TurretMount_Small.effectDescription</t>
+  </si>
+  <si>
+    <t>TB_Upgrade_TurretMount_Small.effectDescription</t>
+  </si>
+  <si>
+    <t>允许安装一座 2x2 大小炮塔。\n\n固定负面效果: -10%载货量, +5%燃料消耗 。1级后每级加成：预热与冷却时间 -25%。</t>
+  </si>
+  <si>
+    <t>正在为穿梭机升级</t>
+  </si>
+  <si>
+    <t>安装升级</t>
+  </si>
+  <si>
+    <t>正在移除穿梭机升级</t>
+  </si>
+  <si>
+    <t>移除升级</t>
+  </si>
+  <si>
+    <t>正在为穿梭机安装炮塔</t>
+  </si>
+  <si>
+    <t>安装炮塔</t>
+  </si>
+  <si>
+    <t>正在移除穿梭机炮塔</t>
+  </si>
+  <si>
+    <t>移除炮塔</t>
+  </si>
+  <si>
+    <t>正在补充穿梭机炮塔弹药</t>
+  </si>
+  <si>
+    <t>补充弹药</t>
+  </si>
+  <si>
+    <t>一架正在飞行中的开拓者号穿梭机。</t>
+  </si>
+  <si>
+    <t>升级</t>
+  </si>
+  <si>
+    <t>升级面板</t>
+  </si>
+  <si>
+    <t>性能</t>
+  </si>
+  <si>
+    <t>防御</t>
+  </si>
+  <si>
+    <t>特殊</t>
+  </si>
+  <si>
+    <t>炮塔</t>
+  </si>
+  <si>
+    <t>电力</t>
+  </si>
+  <si>
+    <t>已安装</t>
+  </si>
+  <si>
+    <t>安装中...</t>
+  </si>
+  <si>
+    <t>拆卸中...</t>
+  </si>
+  <si>
+    <t>互斥</t>
+  </si>
+  <si>
+    <t>未解锁</t>
+  </si>
+  <si>
+    <t>前置需求</t>
+  </si>
+  <si>
+    <t>科技需求：{0}</t>
+  </si>
+  <si>
+    <t>与 {0} 互斥</t>
+  </si>
+  <si>
+    <t>费用</t>
+  </si>
+  <si>
+    <t>费用（Lv.{0}）</t>
+  </si>
+  <si>
+    <t>已达最高等级。</t>
+  </si>
+  <si>
+    <t>当前加成（Lv.{0}）</t>
+  </si>
+  <si>
+    <t>效果</t>
+  </si>
+  <si>
+    <t>进度</t>
+  </si>
+  <si>
+    <t>全图覆盖</t>
+  </si>
+  <si>
+    <t>安装</t>
+  </si>
+  <si>
+    <t>拆卸</t>
+  </si>
+  <si>
+    <t>燃料容量</t>
+  </si>
+  <si>
+    <t>燃料消耗</t>
+  </si>
+  <si>
+    <t>发射距离</t>
+  </si>
+  <si>
+    <t>载重量</t>
+  </si>
+  <si>
+    <t>冷却时间</t>
+  </si>
+  <si>
+    <t>护盾上限</t>
+  </si>
+  <si>
+    <t>护盾充能速率</t>
+  </si>
+  <si>
+    <t>探测半径</t>
+  </si>
+  <si>
+    <t>信号半径</t>
+  </si>
+  <si>
+    <t>跃迁冷却</t>
+  </si>
+  <si>
+    <t>输出功率</t>
+  </si>
+  <si>
+    <t>炮塔预热</t>
+  </si>
+  <si>
+    <t>炮塔冷却</t>
+  </si>
+  <si>
+    <t>飞行速度</t>
+  </si>
+  <si>
+    <t>灵能探测阵列运行中</t>
+  </si>
+  <si>
+    <t>显示探测范围</t>
+  </si>
+  <si>
+    <t>取消升级</t>
+  </si>
+  <si>
+    <t>取消当前的升级或拆卸任务。</t>
+  </si>
+  <si>
+    <t>跃迁引擎</t>
+  </si>
+  <si>
+    <t>将穿梭机传送到本地图上的新位置。</t>
+  </si>
+  <si>
+    <t>冷却中：{0}</t>
+  </si>
+  <si>
+    <t>取消跃迁</t>
+  </si>
+  <si>
+    <t>取消跃迁引擎的充能。</t>
+  </si>
+  <si>
+    <t>选择炮塔</t>
+  </si>
+  <si>
+    <t>选择一个安装在炮塔底座上的炮塔。</t>
+  </si>
+  <si>
+    <t>拆卸炮塔</t>
+  </si>
+  <si>
+    <t>从底座上拆下已安装的炮塔。</t>
+  </si>
+  <si>
+    <t>取消炮塔任务</t>
+  </si>
+  <si>
+    <t>取消正在进行的炮塔安装或拆卸任务。</t>
+  </si>
+  <si>
+    <t>指派殖民者搬运{0}来补充炮塔弹药。</t>
+  </si>
+  <si>
+    <t>弹药</t>
+  </si>
+  <si>
+    <t>弹药已满。</t>
+  </si>
+  <si>
+    <t>消耗弹药不足，暂不需要补充。</t>
+  </si>
+  <si>
+    <t>弹药补充已在等待中。</t>
+  </si>
+  <si>
+    <t>取消补弹</t>
+  </si>
+  <si>
+    <t>取消等待中的弹药补充任务。</t>
+  </si>
+  <si>
+    <t>弹药: {0}</t>
+  </si>
+  <si>
+    <t>切换炮塔使用的弹药类型。</t>
+  </si>
+  <si>
+    <t>所需科技尚未研究完成。</t>
+  </si>
+  <si>
+    <t>资源不足。</t>
+  </si>
+  <si>
+    <t>与已安装的升级互斥。</t>
+  </si>
+  <si>
+    <t>没有兼容的炮塔可用。</t>
+  </si>
+  <si>
+    <t>正在升级：{0}（剩余工作量：{1}）</t>
+  </si>
+  <si>
+    <t>炮塔：{0}</t>
+  </si>
+  <si>
+    <t>跃迁引擎：就绪</t>
+  </si>
+  <si>
+    <t>跃迁引擎：充能中（{0}%）</t>
+  </si>
+  <si>
+    <t>跃迁引擎：冷却中（{0}）</t>
+  </si>
+  <si>
+    <t>护盾</t>
+  </si>
+  <si>
+    <t>恢复中（{0}秒）</t>
+  </si>
+  <si>
+    <t>恢复中</t>
+  </si>
+  <si>
+    <t>启用护盾</t>
+  </si>
+  <si>
+    <t>护盾半径：{0} 格</t>
+  </si>
+  <si>
+    <t>已关闭</t>
+  </si>
+  <si>
+    <t>护盾已关闭</t>
+  </si>
+  <si>
+    <t>充能速率：{0}/s{1}</t>
+  </si>
+  <si>
+    <t>射程</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>正在安装穿梭机升级。</t>
+  </si>
+  <si>
+    <t>엔진 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반중력 기술 모듈을 탑재합니다. \n\n왕복선의 연료 소모율을 줄이는 동시에, 최대 비거리와 적재 용량이 비약적으로 증가합니다.</t>
+  </si>
+  <si>
+    <t>비거리</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>每</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>加成：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>飞</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>行距离 ×1.2，速度 ×1.25，</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>发</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>射冷却</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>减</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>少 1250 tick，燃料消耗 ×1.1。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>항속</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨당 보너스: 비거리 x1.2, 항속 x1.25, 발사 대기시간 -1250틱, 연료 소비량 x1.1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반중력 코어 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호막 코어 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반중력 발전기</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보호막 코어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반중력 코어</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>보조 추진기를 탑재하고 기존 부품을 최적화합니다. \n\n연료 소모량이 다소 증가하는 대신, 최대 비거리와 항속을 대폭 향상시키고 발사 대기시간을 단축합니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨당 보너스: 비거리 x1.05, 적재 용량 x1.25, 연료 소비량 x0.8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>레벨당 보너스: 보호막 최대 용량 +1000, 보호막 충전 속도 +36/초, 보호막 재충전 지연 -5초</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>반중력 발전기 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>정박 시 활성화. 레벨당 보너스: 전력 출력량 +2000W</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>초능력 탐지 배열 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>신호 확장 중계기 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>以穿梭机</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>为</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>中心生成</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>额</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>外的机械族指</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>挥区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>域。\n\n每</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>加成：覆盖半</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>径</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve"> +10 格。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>满级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>（5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>级</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>时</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>覆盖全</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="새굴림"/>
+        <family val="1"/>
+        <charset val="129"/>
+      </rPr>
+      <t>图</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+      </rPr>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>점프 드라이브 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 지도 내 어느 곳이든 단거리 공간 점프를 할 수 있게 됩니다. 업그레이드 시 재사용 대기시간이 추가로 단축됩니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대형 포탑 거치대 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중소형 포탑 거치대</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>대형 거치대를 탑재합니다. \n\n3x3 포탑을 설치할 수 있게 되며 사격 통제 효율 또한 높입니다. 중소형 거치대 업그레이드와 동시에 설치할 수 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중소형 거치대를 탑재합니다. \n\n2x2 포탑을 설치할 수 있게 되며 사격 통제 효율 또한 높입니다. 대형 거치대 업그레이드와 동시에 설치할 수 없습니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>포탑 원거리 재사용 대기시간</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>중소형 포탑 거치대 업그레이드</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3x3 크기의 포탑 1개를 설치할 수 있습니다. 포탑을 설치하면 왕복선의 적재 용량이 20% 감소하고, 연료 소비량이 10% 증가합니다.\n\n레벨당 보너스: 포탑의 조준 시간 및 원거리 재사용 대기시간 -25%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2x2 크기의 포탑 1개를 설치할 수 있습니다. 포탑을 설치하면 왕복선의 적재 용량이 10% 감소하고, 연료 소비량이 5% 증가합니다.\n\n레벨당 보너스: 포탑의 조준 시간 및 원거리 재사용 대기시간 -25%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕복선을 중심으로 추가적인 메카노이드 지휘 영역을 생성합니다. \n\n레벨당 보너스: 신호 반경 +10타일, 최대 레벨(5단계) 달성 시 반경이 무제한이 됩니다.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>왕복선 주변 20타일 반경 내의 은신 유닛을 지속적으로 탐지하여 드러냅니다.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1603,7 +2460,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1619,6 +2476,20 @@
     <font>
       <sz val="8"/>
       <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="새굴림"/>
+      <family val="1"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
     </font>
@@ -1643,14 +2514,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1948,7 +2850,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F131"/>
+  <dimension ref="A1:L149"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="9.140625" style="1" customWidth="1"/>
@@ -2006,10 +2908,10 @@
         <v>11</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -2060,7 +2962,7 @@
         <v>21</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
@@ -2077,7 +2979,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
@@ -2094,7 +2996,7 @@
         <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
@@ -2111,7 +3013,7 @@
         <v>30</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
@@ -2128,7 +3030,7 @@
         <v>34</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
@@ -2145,7 +3047,7 @@
         <v>37</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
@@ -2179,7 +3081,7 @@
         <v>43</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -2196,7 +3098,7 @@
         <v>46</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
@@ -2230,7 +3132,7 @@
         <v>52</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
@@ -2247,7 +3149,7 @@
         <v>55</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2281,7 +3183,7 @@
         <v>60</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
@@ -2298,7 +3200,7 @@
         <v>63</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
@@ -2332,7 +3234,7 @@
         <v>68</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
@@ -2349,7 +3251,7 @@
         <v>71</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>508</v>
+        <v>497</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2383,7 +3285,7 @@
         <v>77</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>510</v>
+        <v>499</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
@@ -2400,7 +3302,7 @@
         <v>80</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>509</v>
+        <v>498</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -2468,7 +3370,7 @@
         <v>93</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>495</v>
+        <v>679</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
@@ -2485,7 +3387,7 @@
         <v>96</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>402</v>
+        <v>678</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
@@ -2502,7 +3404,7 @@
         <v>99</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>496</v>
+        <v>669</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
@@ -2519,7 +3421,7 @@
         <v>102</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>473</v>
+        <v>677</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
@@ -2536,7 +3438,7 @@
         <v>105</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
@@ -2553,7 +3455,7 @@
         <v>108</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>403</v>
+        <v>676</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
@@ -2570,7 +3472,7 @@
         <v>111</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
@@ -2587,7 +3489,7 @@
         <v>114</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
@@ -2604,7 +3506,7 @@
         <v>117</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -2621,7 +3523,7 @@
         <v>120</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2638,7 +3540,7 @@
         <v>123</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
@@ -2655,7 +3557,7 @@
         <v>126</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
@@ -2672,7 +3574,7 @@
         <v>129</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
@@ -2689,7 +3591,7 @@
         <v>132</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
@@ -2706,7 +3608,7 @@
         <v>135</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>499</v>
+        <v>691</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
@@ -2723,7 +3625,7 @@
         <v>138</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>407</v>
+        <v>690</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
@@ -2740,7 +3642,7 @@
         <v>141</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>500</v>
+        <v>692</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -2757,7 +3659,7 @@
         <v>145</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -2774,7 +3676,7 @@
         <v>148</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>501</v>
+        <v>491</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
@@ -2791,7 +3693,7 @@
         <v>151</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -2808,7 +3710,7 @@
         <v>154</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
@@ -2825,7 +3727,7 @@
         <v>157</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
@@ -2842,7 +3744,7 @@
         <v>160</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
@@ -2859,7 +3761,7 @@
         <v>163</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
@@ -2876,7 +3778,7 @@
         <v>166</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
@@ -2893,7 +3795,7 @@
         <v>169</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
@@ -2910,7 +3812,7 @@
         <v>172</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -2927,7 +3829,7 @@
         <v>175</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -2944,7 +3846,7 @@
         <v>178</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -2961,7 +3863,7 @@
         <v>181</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -2978,7 +3880,7 @@
         <v>184</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
@@ -2995,7 +3897,7 @@
         <v>187</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
@@ -3012,7 +3914,7 @@
         <v>190</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
@@ -3029,7 +3931,7 @@
         <v>193</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
@@ -3046,7 +3948,7 @@
         <v>196</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
@@ -3063,7 +3965,7 @@
         <v>199</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
@@ -3080,7 +3982,7 @@
         <v>202</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
@@ -3097,7 +3999,7 @@
         <v>205</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
@@ -3114,7 +4016,7 @@
         <v>208</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
@@ -3165,7 +4067,7 @@
         <v>217</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>480</v>
+        <v>475</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3182,7 +4084,7 @@
         <v>220</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
@@ -3199,7 +4101,7 @@
         <v>223</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>502</v>
+        <v>670</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
@@ -3216,7 +4118,7 @@
         <v>226</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3233,7 +4135,7 @@
         <v>229</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
@@ -3250,7 +4152,7 @@
         <v>232</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>479</v>
+        <v>474</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3267,7 +4169,7 @@
         <v>235</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
@@ -3284,7 +4186,7 @@
         <v>238</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
@@ -3301,7 +4203,7 @@
         <v>241</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
@@ -3318,7 +4220,7 @@
         <v>244</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>481</v>
+        <v>476</v>
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
@@ -3335,7 +4237,7 @@
         <v>247</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
@@ -3352,7 +4254,7 @@
         <v>250</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
@@ -3369,7 +4271,7 @@
         <v>253</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>430</v>
+        <v>693</v>
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
@@ -3386,7 +4288,7 @@
         <v>256</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>482</v>
+        <v>672</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
@@ -3403,7 +4305,7 @@
         <v>259</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
@@ -3420,7 +4322,7 @@
         <v>262</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
@@ -3437,7 +4339,7 @@
         <v>265</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
@@ -3454,7 +4356,7 @@
         <v>268</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
@@ -3471,7 +4373,7 @@
         <v>271</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
@@ -3488,7 +4390,7 @@
         <v>274</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
@@ -3505,7 +4407,7 @@
         <v>277</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
@@ -3522,7 +4424,7 @@
         <v>280</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
@@ -3539,7 +4441,7 @@
         <v>283</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
@@ -3556,7 +4458,7 @@
         <v>286</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
@@ -3573,7 +4475,7 @@
         <v>289</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
@@ -3590,7 +4492,7 @@
         <v>292</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
@@ -3607,7 +4509,7 @@
         <v>295</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
@@ -3624,7 +4526,7 @@
         <v>298</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
@@ -3641,7 +4543,7 @@
         <v>301</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
@@ -3675,7 +4577,7 @@
         <v>306</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
@@ -3692,7 +4594,7 @@
         <v>309</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
@@ -3709,7 +4611,7 @@
         <v>312</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
@@ -3726,7 +4628,7 @@
         <v>315</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
@@ -3743,7 +4645,7 @@
         <v>318</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
@@ -3760,7 +4662,7 @@
         <v>321</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
@@ -3777,7 +4679,7 @@
         <v>324</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
@@ -3794,7 +4696,7 @@
         <v>327</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
@@ -3811,7 +4713,7 @@
         <v>330</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
@@ -3828,7 +4730,7 @@
         <v>333</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
@@ -3845,7 +4747,7 @@
         <v>336</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
@@ -3862,7 +4764,7 @@
         <v>339</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
@@ -3879,7 +4781,7 @@
         <v>342</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
@@ -3896,7 +4798,7 @@
         <v>345</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
@@ -3913,7 +4815,7 @@
         <v>348</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
@@ -3930,7 +4832,7 @@
         <v>351</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
@@ -3947,7 +4849,7 @@
         <v>354</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
@@ -3964,7 +4866,7 @@
         <v>357</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
@@ -3981,7 +4883,7 @@
         <v>360</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
@@ -3998,7 +4900,7 @@
         <v>363</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
@@ -4032,7 +4934,7 @@
         <v>369</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
@@ -4049,7 +4951,7 @@
         <v>372</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
@@ -4066,7 +4968,7 @@
         <v>375</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>476</v>
+        <v>471</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
@@ -4083,7 +4985,7 @@
         <v>378</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>477</v>
+        <v>472</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
@@ -4100,7 +5002,7 @@
         <v>381</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
@@ -4117,7 +5019,7 @@
         <v>384</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>478</v>
+        <v>473</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
@@ -4134,10 +5036,10 @@
         <v>387</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A129" s="1" t="s">
         <v>388</v>
       </c>
@@ -4151,10 +5053,10 @@
         <v>390</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A130" s="1" t="s">
         <v>391</v>
       </c>
@@ -4168,10 +5070,10 @@
         <v>229</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A131" s="1" t="s">
         <v>393</v>
       </c>
@@ -4185,11 +5087,3809 @@
         <v>394</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>461</v>
-      </c>
+        <v>457</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D132" s="2"/>
+      <c r="E132" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="F132" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="G132" s="2"/>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2"/>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D133" s="2"/>
+      <c r="E133" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="F133" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="G133" s="2"/>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D134" s="2"/>
+      <c r="E134" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F134" s="1" t="s">
+        <v>674</v>
+      </c>
+      <c r="G134" s="2"/>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="D135" s="2"/>
+      <c r="E135" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F135" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="G135" s="2"/>
+      <c r="H135" s="2"/>
+      <c r="I135" s="2"/>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="D136" s="2"/>
+      <c r="E136" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F136" s="1" t="s">
+        <v>675</v>
+      </c>
+      <c r="G136" s="2"/>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="D137" s="2"/>
+      <c r="E137" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="F137" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="G137" s="2"/>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D138" s="2"/>
+      <c r="E138" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="F138" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="G138" s="2"/>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D139" s="2"/>
+      <c r="E139" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="F139" s="1" t="s">
+        <v>683</v>
+      </c>
+      <c r="G139" s="2"/>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2"/>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="D140" s="2"/>
+      <c r="E140" s="2" t="s">
+        <v>540</v>
+      </c>
+      <c r="F140" s="1" t="s">
+        <v>684</v>
+      </c>
+      <c r="G140" s="2"/>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2"/>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="D141" s="2"/>
+      <c r="E141" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="F141" s="1" t="s">
+        <v>698</v>
+      </c>
+      <c r="G141" s="2"/>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="D142" s="2"/>
+      <c r="E142" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F142" s="1" t="s">
+        <v>685</v>
+      </c>
+      <c r="G142" s="2"/>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="D143" s="2"/>
+      <c r="E143" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="F143" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="G143" s="2"/>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="D144" s="2"/>
+      <c r="E144" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="F144" s="1" t="s">
+        <v>687</v>
+      </c>
+      <c r="G144" s="2"/>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2"/>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="D145" s="2"/>
+      <c r="E145" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="F145" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="G145" s="2"/>
+      <c r="H145" s="2"/>
+      <c r="I145" s="2"/>
+      <c r="J145" s="2"/>
+      <c r="K145" s="2"/>
+      <c r="L145" s="2"/>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="D146" s="2"/>
+      <c r="E146" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="F146" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="G146" s="2"/>
+      <c r="H146" s="2"/>
+      <c r="I146" s="2"/>
+      <c r="J146" s="2"/>
+      <c r="K146" s="2"/>
+      <c r="L146" s="2"/>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="D147" s="2"/>
+      <c r="E147" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="F147" s="1" t="s">
+        <v>695</v>
+      </c>
+      <c r="G147" s="2"/>
+      <c r="H147" s="2"/>
+      <c r="I147" s="2"/>
+      <c r="J147" s="2"/>
+      <c r="K147" s="2"/>
+      <c r="L147" s="2"/>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="D148" s="2"/>
+      <c r="E148" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="F148" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="G148" s="2"/>
+      <c r="H148" s="2"/>
+      <c r="I148" s="2"/>
+      <c r="J148" s="2"/>
+      <c r="K148" s="2"/>
+      <c r="L148" s="2"/>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A149" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B149" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C149" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="D149" s="2"/>
+      <c r="E149" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="F149" s="1" t="s">
+        <v>696</v>
+      </c>
+      <c r="G149" s="2"/>
+      <c r="H149" s="2"/>
+      <c r="I149" s="2"/>
+      <c r="J149" s="2"/>
+      <c r="K149" s="2"/>
+      <c r="L149" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
+  <conditionalFormatting sqref="A132:A149">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>COUNTIF($A:$A, A132)=0</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B48163-495B-4196-9777-33C19B4C8DB1}">
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:F148"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="58.7109375" style="2" customWidth="1"/>
+    <col min="2" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>573</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>581</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>595</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>596</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B88" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C88" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C89" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B92" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C92" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>623</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B104" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C104" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B105" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C105" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B106" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C106" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B107" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C107" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B109" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C109" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B110" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C110" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B111" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C111" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F111" s="2" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B112" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C112" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F112" s="2" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B113" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C113" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F113" s="2" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B114" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C114" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F114" s="2" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B115" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C115" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F115" s="2" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B116" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C116" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F116" s="2" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B117" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C117" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F117" s="2" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B118" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C118" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F118" s="2" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B119" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C119" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F119" s="2" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B120" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C120" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F120" s="2" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A121" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B121" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C121" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F121" s="2" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B122" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C122" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F122" s="2" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B123" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C123" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F123" s="2" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A124" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B124" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C124" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F124" s="2" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A125" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B125" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C125" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F125" s="2" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A126" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B126" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C126" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F126" s="2" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B127" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C127" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F127" s="2" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A128" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B128" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C128" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F128" s="2" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B129" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C129" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F129" s="2" t="s">
+        <v>649</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B130" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C130" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F130" s="2" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B131" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C131" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F131" s="2" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B132" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C132" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F132" s="2" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B133" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C133" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F133" s="2" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B134" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C134" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F134" s="2" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B135" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C135" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F135" s="2" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B136" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C136" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F136" s="2" t="s">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B137" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C137" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F137" s="2" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B138" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C138" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F138" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A139" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B139" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C139" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F139" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A140" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B140" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C140" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F140" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A141" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B141" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C141" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F141" s="2" t="s">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A142" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B142" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C142" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F142" s="2" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A143" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B143" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C143" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F143" s="2" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A144" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B144" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C144" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F144" s="2" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A145" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B145" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C145" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F145" s="2" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A146" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B146" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F146" s="2" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A147" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B147" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F147" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" hidden="1" x14ac:dyDescent="0.3">
+      <c r="A148" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B148" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C148" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F148" s="2" t="s">
+        <v>667</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:A148" xr:uid="{E2B48163-495B-4196-9777-33C19B4C8DB1}">
+    <filterColumn colId="0">
+      <colorFilter dxfId="3"/>
+    </filterColumn>
+  </autoFilter>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{F84AC72E-A160-4606-86DE-1B03B556916B}">
+            <xm:f>COUNTIF(Sheet1!$A:$A, A1)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A1:A1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{458B3012-A002-4F17-8FF1-0B13FA6C117F}">
+  <dimension ref="A1:F86"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="16384" width="9.140625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B32" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="B33" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C33" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B34" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="B43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="B45" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B46" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="B47" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B48" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="B49" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="B51" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B52" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B53" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B54" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B55" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="B56" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C56" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B57" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B58" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B59" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B60" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C60" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B61" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B62" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B63" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B64" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B68" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A69" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B69" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A70" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B70" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B71" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A72" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B72" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A73" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B73" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A74" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="B74" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A75" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B75" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="B76" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A78" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B78" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A79" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B79" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A80" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A83" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A84" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A86" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
+      <x14:conditionalFormattings>
+        <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+          <x14:cfRule type="expression" priority="1" id="{79FB29D9-6ADD-42FB-999A-4A2472E63D52}">
+            <xm:f>COUNTIF(Sheet1!$A:$A, A1)=0</xm:f>
+            <x14:dxf>
+              <fill>
+                <patternFill>
+                  <bgColor rgb="FFFFFF00"/>
+                </patternFill>
+              </fill>
+            </x14:dxf>
+          </x14:cfRule>
+          <xm:sqref>A1:A1048576</xm:sqref>
+        </x14:conditionalFormatting>
+      </x14:conditionalFormattings>
+    </ext>
+  </extLst>
+</worksheet>
 </file>